--- a/public/exports-from-60-with-coowners/29189641.xlsx
+++ b/public/exports-from-60-with-coowners/29189641.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311437743</t>
+          <t xml:space="preserve">311478273</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189641.xlsx
+++ b/public/exports-from-60-with-coowners/29189641.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012235</t>
+          <t xml:space="preserve">200012236</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012231</t>
+          <t xml:space="preserve">200012236</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189641.xlsx
+++ b/public/exports-from-60-with-coowners/29189641.xlsx
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012236</t>
+          <t xml:space="preserve">200012235</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012236</t>
+          <t xml:space="preserve">200012231</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311478273</t>
+          <t xml:space="preserve">311437743</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
